--- a/term/ValueSet-KLConditionCodes.xlsx
+++ b/term/ValueSet-KLConditionCodes.xlsx
@@ -34,7 +34,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>2.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-31T13:18:46+01:00</t>
+    <t>2025-08-21T08:46:07+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/term/ValueSet-KLConditionCodes.xlsx
+++ b/term/ValueSet-KLConditionCodes.xlsx
@@ -34,7 +34,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.3.0</t>
+    <t>2.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-21T08:46:07+02:00</t>
+    <t>2026-04-21T22:08:40+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
